--- a/output/pdf_financials_xlsx/HMMC.xlsx
+++ b/output/pdf_financials_xlsx/HMMC.xlsx
@@ -1122,10 +1122,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.255</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.216</v>
       </c>
       <c r="D34" s="1" t="inlineStr">
         <is>
@@ -1158,10 +1158,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.255</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.216</v>
       </c>
       <c r="D36" s="1" t="inlineStr">
         <is>
@@ -3109,7 +3109,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">

--- a/output/pdf_financials_xlsx/HMMC.xlsx
+++ b/output/pdf_financials_xlsx/HMMC.xlsx
@@ -4478,7 +4478,11 @@
           <t>Deferred income tax expense 15 5,733</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
           <t>-</t>
@@ -4748,7 +4752,11 @@
           <t>Proceeds from private placement 18 2,751</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
           <t>-</t>
